--- a/0_External_data/DeDuCE_rework/tms_f_initial_shocks_DeDuCE.xlsx
+++ b/0_External_data/DeDuCE_rework/tms_f_initial_shocks_DeDuCE.xlsx
@@ -1,155 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="OLD_current_file" sheetId="2" r:id="rId2"/>
-    <sheet name="AVE_pha400" sheetId="3" r:id="rId3"/>
-    <sheet name="AVE_pha2000" sheetId="4" r:id="rId4"/>
-    <sheet name="AVE_pha10000" sheetId="5" r:id="rId5"/>
-    <sheet name="AVE_co2_50" sheetId="6" r:id="rId6"/>
-    <sheet name="AVE_co2_100" sheetId="7" r:id="rId7"/>
-    <sheet name="AVE_co2_190" sheetId="8" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLD_current_file" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_pha400" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_pha2000" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_pha10000" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_co2_50" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_co2_100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_co2_190" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVE_pha0" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="37">
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Same layout as tms_f_initial_shocks.xlsx (Country rows, sector columns), values = 100 x AVE (ad-valorem equivalent, %).</t>
-  </si>
-  <si>
-    <t>AVE = p_ha x h_total; h_total = embodied deforestation per $ of output (DeDuCE amortised 2018-2023, domestic Leontief) -&gt; h_table_DeDuCE.xlsx.</t>
-  </si>
-  <si>
-    <t>Destination-independent (ignores the base tariff t0). The exact tms_f shock is 100 x AVE/(1+t0), given bilaterally in tms_f_shocks_bilateral_*.csv.</t>
-  </si>
-  <si>
-    <t>Pasture deforestation is split across ruminant, rmk and wol by their AEZ land-rent shares (no double counting); dairy carries rmk's share via the Leontief pass.</t>
-  </si>
-  <si>
-    <t>New columns RuminantMeat, dairy, vegoil, lea, pdr, c_b: list_commodity in rework_functions.R includes them.</t>
-  </si>
-  <si>
-    <t>Sheet OLD_current_file = the file the model uses today.</t>
-  </si>
-  <si>
-    <t>sgr</t>
-  </si>
-  <si>
-    <t>ruminant</t>
-  </si>
-  <si>
-    <t>gro</t>
-  </si>
-  <si>
-    <t>ocr</t>
-  </si>
-  <si>
-    <t>osd</t>
-  </si>
-  <si>
-    <t>pcr</t>
-  </si>
-  <si>
-    <t>pfb</t>
-  </si>
-  <si>
-    <t>v_f</t>
-  </si>
-  <si>
-    <t>wht</t>
-  </si>
-  <si>
-    <t>rmk</t>
-  </si>
-  <si>
-    <t>wol</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>brasil</t>
-  </si>
-  <si>
-    <t>indonesia</t>
-  </si>
-  <si>
-    <t>argentina</t>
-  </si>
-  <si>
-    <t>bolivia</t>
-  </si>
-  <si>
-    <t>colombia</t>
-  </si>
-  <si>
-    <t>angola</t>
-  </si>
-  <si>
-    <t>ghana</t>
-  </si>
-  <si>
-    <t>ivorycoast</t>
-  </si>
-  <si>
-    <t>malasya</t>
-  </si>
-  <si>
-    <t>paraguay</t>
-  </si>
-  <si>
-    <t>peru</t>
-  </si>
-  <si>
-    <t>drc</t>
-  </si>
-  <si>
-    <t>RuminantMeat</t>
-  </si>
-  <si>
-    <t>dairy</t>
-  </si>
-  <si>
-    <t>vegoil</t>
-  </si>
-  <si>
-    <t>lea</t>
-  </si>
-  <si>
-    <t>pdr</t>
-  </si>
-  <si>
-    <t>c_b</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,13 +54,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -462,43 +415,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Same layout as tms_f_initial_shocks.xlsx (Country rows, sector columns), values = 100 x AVE (ad-valorem equivalent, %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AVE = p_ha x h_total; h_total = embodied deforestation per $ of output (DeDuCE amortised 2018-2023, domestic Leontief) -&gt; h_table_DeDuCE.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Destination-independent (ignores the base tariff t0). The exact tms_f shock is 100 x AVE/(1+t0), given bilaterally in tms_f_shocks_bilateral_*.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pasture deforestation is split across ruminant, rmk and wol by their AEZ land-rent shares (no double counting); dairy carries rmk's share via the Leontief pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>New columns RuminantMeat, dairy, vegoil, lea, pdr, c_b: list_commodity in rework_functions.R includes them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sheet OLD_current_file = the file the model uses today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AVE_pha0: no footprint charge (every value 0). With tau &gt; 0 it gives a pure club penalty - every non-member pays the flat tau on the 17 sectors, deforestation or not.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -507,501 +485,553 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H13" t="n">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
-        <v>1.1</v>
-      </c>
-      <c r="C2">
-        <v>1.1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>1.6</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>0.4</v>
-      </c>
-      <c r="H2">
-        <v>2.6</v>
-      </c>
-      <c r="I2">
-        <v>1.2</v>
-      </c>
-      <c r="J2">
-        <v>1.4</v>
-      </c>
-      <c r="K2">
-        <v>1.1</v>
-      </c>
-      <c r="L2">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>0.9</v>
-      </c>
-      <c r="C3">
-        <v>0.7</v>
-      </c>
-      <c r="D3">
-        <v>5.5</v>
-      </c>
-      <c r="E3">
-        <v>1.3</v>
-      </c>
-      <c r="F3">
-        <v>4.8</v>
-      </c>
-      <c r="G3">
-        <v>0.4</v>
-      </c>
-      <c r="H3">
-        <v>12.9</v>
-      </c>
-      <c r="I3">
-        <v>0.7</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0.7</v>
-      </c>
-      <c r="L3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-      <c r="C4">
-        <v>4.3</v>
-      </c>
-      <c r="D4">
-        <v>2.5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1.3</v>
-      </c>
-      <c r="G4">
-        <v>1.8</v>
-      </c>
-      <c r="H4">
-        <v>1.6</v>
-      </c>
-      <c r="I4">
+      <c r="I13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.8</v>
       </c>
-      <c r="J4">
-        <v>0.8</v>
-      </c>
-      <c r="K4">
-        <v>4.3</v>
-      </c>
-      <c r="L4">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>3.3</v>
-      </c>
-      <c r="C5">
-        <v>1.4</v>
-      </c>
-      <c r="D5">
-        <v>15.7</v>
-      </c>
-      <c r="E5">
-        <v>3.7</v>
-      </c>
-      <c r="F5">
-        <v>4.2</v>
-      </c>
-      <c r="G5">
-        <v>3.9</v>
-      </c>
-      <c r="H5">
-        <v>10.2</v>
-      </c>
-      <c r="I5">
-        <v>2.7</v>
-      </c>
-      <c r="J5">
-        <v>4.9</v>
-      </c>
-      <c r="K5">
-        <v>1.4</v>
-      </c>
-      <c r="L5">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>1.9</v>
-      </c>
-      <c r="C6">
-        <v>1.5</v>
-      </c>
-      <c r="D6">
-        <v>4.1</v>
-      </c>
-      <c r="E6">
-        <v>3.9</v>
-      </c>
-      <c r="F6">
-        <v>6.8</v>
-      </c>
-      <c r="G6">
-        <v>2.5</v>
-      </c>
-      <c r="H6">
-        <v>2.2</v>
-      </c>
-      <c r="I6">
-        <v>3.6</v>
-      </c>
-      <c r="J6">
-        <v>4.4</v>
-      </c>
-      <c r="K6">
-        <v>1.5</v>
-      </c>
-      <c r="L6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>0.6</v>
-      </c>
-      <c r="C7">
-        <v>2.9</v>
-      </c>
-      <c r="D7">
-        <v>10.9</v>
-      </c>
-      <c r="E7">
-        <v>1.2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>0.7</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0.3</v>
-      </c>
-      <c r="K7">
-        <v>2.9</v>
-      </c>
-      <c r="L7">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>2.2</v>
-      </c>
-      <c r="C8">
-        <v>2.6</v>
-      </c>
-      <c r="D8">
-        <v>3.7</v>
-      </c>
-      <c r="E8">
-        <v>6.3</v>
-      </c>
-      <c r="F8">
-        <v>5.7</v>
-      </c>
-      <c r="G8">
-        <v>6.7</v>
-      </c>
-      <c r="H8">
-        <v>9.1</v>
-      </c>
-      <c r="I8">
-        <v>6.2</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>2.6</v>
-      </c>
-      <c r="L8">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>13.2</v>
-      </c>
-      <c r="C9">
-        <v>14.6</v>
-      </c>
-      <c r="D9">
-        <v>18.6</v>
-      </c>
-      <c r="E9">
-        <v>27.9</v>
-      </c>
-      <c r="F9">
-        <v>20.9</v>
-      </c>
-      <c r="G9">
-        <v>15.1</v>
-      </c>
-      <c r="H9">
-        <v>21.3</v>
-      </c>
-      <c r="I9">
-        <v>22.6</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>14.6</v>
-      </c>
-      <c r="L9">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
-        <v>18.3</v>
-      </c>
-      <c r="C10">
-        <v>0.3</v>
-      </c>
-      <c r="D10">
-        <v>1.3</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>2.3</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>17.1</v>
-      </c>
-      <c r="I10">
-        <v>3.6</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.3</v>
-      </c>
-      <c r="L10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
-        <v>3.1</v>
-      </c>
-      <c r="C11">
-        <v>2.9</v>
-      </c>
-      <c r="D11">
-        <v>18.4</v>
-      </c>
-      <c r="E11">
-        <v>7.3</v>
-      </c>
-      <c r="F11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G11">
-        <v>24.2</v>
-      </c>
-      <c r="H11">
-        <v>12.5</v>
-      </c>
-      <c r="I11">
-        <v>5.7</v>
-      </c>
-      <c r="J11">
-        <v>5.6</v>
-      </c>
-      <c r="K11">
-        <v>2.9</v>
-      </c>
-      <c r="L11">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
-        <v>2.4</v>
-      </c>
-      <c r="C12">
-        <v>3.6</v>
-      </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-      <c r="E12">
-        <v>12.3</v>
-      </c>
-      <c r="F12">
-        <v>10.7</v>
-      </c>
-      <c r="G12">
-        <v>2.8</v>
-      </c>
-      <c r="H12">
-        <v>9.5</v>
-      </c>
-      <c r="I12">
-        <v>4.7</v>
-      </c>
-      <c r="J12">
-        <v>2.8</v>
-      </c>
-      <c r="K12">
-        <v>3.6</v>
-      </c>
-      <c r="L12">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
-        <v>1.2</v>
-      </c>
-      <c r="C13">
-        <v>0.8</v>
-      </c>
-      <c r="D13">
-        <v>4.6</v>
-      </c>
-      <c r="E13">
-        <v>14.5</v>
-      </c>
-      <c r="F13">
-        <v>9.9</v>
-      </c>
-      <c r="G13">
-        <v>2.9</v>
-      </c>
-      <c r="H13">
-        <v>15</v>
-      </c>
-      <c r="I13">
-        <v>4.5</v>
-      </c>
-      <c r="J13">
-        <v>3.7</v>
-      </c>
-      <c r="K13">
-        <v>0.8</v>
-      </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1011,735 +1041,799 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.0293</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1.5431</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.0311</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.0227</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>0.1412</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.0068</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.007</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>0.0129</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0.0337</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>1.5077</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>1.1185</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>0.8102</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>0.4991</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>0.0352</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>0.0225</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>0.0616</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.0505</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>0.1247</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.0298</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0.0955</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>0.3168</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>0.0226</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>0.0151</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>0.06</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>0.066</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>0.1112</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>0.0866</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>0.0349</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>0.0339</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>0.0953</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.0013</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>0.0432</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>0.08890000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.0221</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>0.0917</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.1216</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0.0983</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.0341</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.0366</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.0154</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>0.2312</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>0.0968</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>0.1024</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>0.051</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>0.0292</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>0.0298</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.0072</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.0056</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>0.0437</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0.1396</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>2.1774</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1.2367</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.1487</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.3818</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>0.7632</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1.1259</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>0.3015</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>4.0801</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>1.5882</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>1.485</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>1.5493</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>0.8903</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>0.965</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>0.1155</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>1.2017</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>0.2569</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0.0491</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>0.3253</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>1.1551</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0.1358</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0.1259</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>0.1158</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0.1368</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>0.1278</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>0.0353</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>0.3408</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>0.3365</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>0.1673</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>0.107</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>0.0727</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>0.0221</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>0.2127</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>0.083</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0.0264</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>2.4339</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>0.2922</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0.0437</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>0.1528</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>0.0551</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>0.3204</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>0.0203</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>2.7176</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>2.3936</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>0.7096</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>0.5244</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>0.7157</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>0.0883</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.0053</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>0.1889</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>0.3231</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0.0455</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1.3784</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>0.7527</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>0.5132</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>0.0958</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>0.0877</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.0015</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.0069</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>0.9163</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>0.5491</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>0.1317</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>0.3323</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.0012</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.0017</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>0.6734</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>0.0423</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0.2443</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>0.5928</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>0.5203</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>0.9405</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>0.6722</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>0.2352</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>0.2766</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>0.4212</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0005</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>0.7379</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>0.6016</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>0.2139</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.0136</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.0178</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>0.1337</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>0.0163</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>0.608</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.0092</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>0.2781</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>0.045</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>0.0045</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>0.0009</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>0.3243</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>0.0293</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>0.1526</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>0.0157</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>0.1024</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>0.0118</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>0.0514</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>0.0047</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>0.0507</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>2.2067</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>1.0696</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1.0734</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>0.2516</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>0.8408</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>0.1563</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>0.2963</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>2.3124</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>1.5725</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>0.7357</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>0.2014</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>0.1531</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.013</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>1.151</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>0.1454</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>0.0318</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>0.2546</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>0.196</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>0.578</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.5301</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>0.1313</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>0.2649</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>0.1283</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>0.0595</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>0.3606</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>0.235</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>0.2367</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>0.065</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>0.0861</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>0.0158</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>0.2393</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>0.0438</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>0.144</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>7.4554</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>4.1193</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>4.0408</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>0.4738</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>3.0121</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>0.5231</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>0.6657</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>0.0293</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>6.8901</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>5.1603</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>1.6259</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>0.2454</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>0.2578</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>0.0785</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>3.167</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -1749,735 +1843,799 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.1466</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>7.7157</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.1555</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.1134</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>0.7059</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.0341</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.0351</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>0.0643</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0.1686</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>7.5387</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>5.5925</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>4.051</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>2.4957</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>0.1758</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>0.3958</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>0.1127</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>0.3082</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.2525</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>0.6237</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.1489</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0.4777</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1.5841</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>0.1132</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>0.0755</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>0.3001</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>0.3298</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>0.5561</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>0.433</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>0.1744</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>0.1693</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>0.4763</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.0064</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>0.2158</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>0.4444</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.1106</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>0.4585</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.6081</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0.4913</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.1706</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.1832</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>0.396</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.07679999999999999</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>1.1561</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>0.4839</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>0.512</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>0.2549</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>0.1461</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>0.1488</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.036</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.0281</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>0.2184</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0.698</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>10.8869</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>6.1833</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.7433</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>6.9088</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3.8162</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>5.6297</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1.5076</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>20.4006</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>7.9411</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>7.4252</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>7.7464</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>4.4513</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>4.8252</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>0.5775</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>6.0085</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>1.2844</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0.2454</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1.6264</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5.7755</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0.6788</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0.6297</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>0.5788</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>0.639</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>0.1763</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1.7039</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1.6827</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>0.8365</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>0.5352</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>0.3635</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>0.1105</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1.0637</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>0.4152</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0.1321</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>12.1695</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1.4609</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0.2186</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>0.7641</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>0.2757</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>1.6018</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>0.1017</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>13.588</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>11.9681</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>3.5479</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>2.622</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>3.5784</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>0.4415</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.0264</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>0.9443</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>1.6154</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0.2275</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>6.8918</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3.7637</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>2.566</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>0.4791</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>0.4383</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.0076</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>0.3381</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.0343</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>4.5817</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>2.7454</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>0.6585</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>1.6617</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.0061</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>3.3668</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>0.2114</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1.2216</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>2.964</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>2.6013</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>4.7025</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>3.3611</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.1762</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>1.3829</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>2.106</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0026</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>3.6897</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>3.0078</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>1.0696</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.0679</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.08890000000000001</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.0437</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>0.6684</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>0.08169999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>0.0479</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>3.0399</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.0029</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.0459</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1.3904</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>0.2252</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>0.0028</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>0.0223</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>0.0047</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>1.6217</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>0.1467</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>0.763</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>0.07870000000000001</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>0.512</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>0.0591</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>0.257</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>0.0233</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>0.2534</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>11.0337</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>5.3478</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>5.3669</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1.2582</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>3.4652</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>4.2041</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>0.7814</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>1.4817</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>11.5621</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>7.8627</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>3.6787</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>1.0071</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>0.7655</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.0649</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>5.7548</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>0.7272</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>0.1588</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1.2731</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>0.9802</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>2.8899</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>7.6505</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>0.6567</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1.3244</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>0.6413</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>0.2975</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>1.8029</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>1.1748</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>1.1834</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>0.325</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>0.4305</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>0.0791</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>1.1966</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>0.2188</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>0.7202</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>37.277</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>20.5966</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>20.2042</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>2.3688</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>15.0607</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>2.6153</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>3.3284</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>0.1464</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>34.4507</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>25.8017</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>8.1294</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>1.2272</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>1.2889</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>0.3925</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>15.8352</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>0.8322000000000001</v>
       </c>
     </row>
@@ -2487,735 +2645,799 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.7329</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>38.5784</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.7774</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.5671</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>3.5293</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.1705</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.1757</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>0.3213</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0.843</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>37.6933</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>27.9626</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>20.2548</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>12.4784</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>0.8792</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>1.979</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>0.5633</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1.5408</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1.2625</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>3.1186</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.7443</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>2.3883</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>7.9206</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>0.5662</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>0.3774</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>1.5005</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>1.6491</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>2.7805</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>2.1651</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>0.872</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>0.8465</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>2.3817</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.032</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>1.0789</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>2.222</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.5532</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>2.2927</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>3.0403</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>2.4566</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.8532</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.9161</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1.9801</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.3839</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>5.7807</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2.4196</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2.5598</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>1.2745</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>0.7302999999999999</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>0.7439</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.1406</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>1.092</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>3.49</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>54.4345</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>30.9167</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>3.7164</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>34.5439</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>19.081</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>28.1485</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>7.5382</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>102.003</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>39.7054</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>37.126</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>38.7321</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>22.2563</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>24.126</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>2.8877</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>30.0424</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>6.4222</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1.2271</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>8.132099999999999</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>28.8777</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3.3939</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>3.1485</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>2.8939</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>3.4201</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>3.1951</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>0.8815</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>8.5197</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>8.4137</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>4.1826</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>2.6758</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>1.8173</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>0.5525</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>5.3185</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>2.0758</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0.6604</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>60.8473</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>7.3046</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1.0931</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>3.8204</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.3787</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>8.008800000000001</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>67.93980000000001</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>59.8405</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>17.7393</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>13.11</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>17.8921</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>2.2074</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.1321</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>4.7216</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>8.077199999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1.1375</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>34.4591</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>18.8183</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>12.8302</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2.3956</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>2.1916</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.0381</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>1.6903</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.1717</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>22.9083</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>13.727</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>3.2927</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>8.308299999999999</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.0305</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.0437</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>16.834</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>1.0572</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>6.1079</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>14.8202</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>13.0063</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>23.5126</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>16.8055</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>5.8811</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>6.9147</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>10.5298</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0128</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>18.4487</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>15.0391</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>5.3482</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.3394</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.4445</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.2184</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>3.3418</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>0.4086</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>0.2394</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>15.1993</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.0147</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.2294</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>6.9521</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.1262</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>0.0142</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>0.1116</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>0.0234</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>8.1083</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>0.7333</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>3.815</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>0.3934</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>2.5601</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>0.2957</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1.2852</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>0.1165</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1.2668</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>55.1686</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>26.739</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>26.8345</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>6.2912</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>17.3258</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>21.0206</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>3.9069</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>7.4086</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>57.8104</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>39.3133</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>18.3934</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>5.0355</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>3.8273</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.3245</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>28.7739</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>3.6362</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>0.7939000000000001</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>6.3655</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>4.9012</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>14.4497</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>38.2525</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>3.2835</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>6.6218</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>3.2067</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>1.4874</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>9.0143</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>5.874</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>5.917</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>1.6252</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>2.1524</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>0.3957</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>5.983</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>1.0938</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>3.6011</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>186.3851</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>102.9828</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>101.0208</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>11.8439</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>75.30329999999999</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>13.0767</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>16.6422</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>0.732</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>172.2536</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>129.0087</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>40.6471</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>6.1359</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>6.4444</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>1.9623</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>79.17619999999999</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>4.1608</v>
       </c>
     </row>
@@ -3225,735 +3447,799 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.8764</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>99.05889999999999</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1.3483</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.7779</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>5.5236</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.3664</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.4302</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>0.549</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1.275</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>96.78279999999999</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>71.7718</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>52.0063</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>32.0358</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>1.399</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>5.0762</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>1.1546</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1.8079</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>6.7598</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>10.7543</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>6.7963</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>5.4595</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>36.9526</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>2.0943</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>2.5031</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>7.0129</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>3.8062</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>9.813700000000001</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>7.7462</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>3.0253</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>3.5684</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>11.1126</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.1169</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>3.9013</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>12.1088</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.4469</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1.9516</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>2.9685</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>4.777</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.8822</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.8986</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1.9629</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.3827</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>5.6265</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2.0534</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2.0478</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>1.0972</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>0.6229</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>0.7639</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.1561</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.1746</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>0.8669</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>7.7728</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>102.9625</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>72.82129999999999</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>7.8742</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>58.3157</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>42.5322</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>67.61239999999999</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>17.1697</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>243.3084</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>75.2184</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>71.199</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>73.32380000000001</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>42.288</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>41.0061</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>5.6442</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>68.5228</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>14.6878</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>3.8645</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>23.4416</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>90.3443</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>6.8081</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>3.0747</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>8.7316</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>11.1508</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>9.6328</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>2.6647</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>24.5571</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>24.2418</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>12.0044</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>7.6729</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>2.5102</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1.575</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>17.413</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>7.687</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0.6781</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>93.1825</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>8.670299999999999</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1.3828</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>4.361</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>2.4735</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>8.778499999999999</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>0.62</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>81.6499</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>91.6332</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>26.915</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>20.0643</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>27.3822</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>2.53</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.1965</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>8.561299999999999</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>7.0236</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1.1747</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>45.5897</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>29.8463</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>6.6381</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2.1281</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>3.4096</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.0568</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>2.699</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.2713</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>30.2428</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>17.7724</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>4.386</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>10.9969</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.0284</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.0574</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>27.0156</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>1.51</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>13.3158</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>20.452</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>31.7983</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>2.2316</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>12.702</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>15.155</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>23.0273</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0058</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>12.0901</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>20.6859</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>7.3417</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.228</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.0633</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.08450000000000001</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>6.7046</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>0.9811</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>0.9282</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>51.3047</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.0492</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>14.4117</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>14.914</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.665</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1.8158</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>9.870799999999999</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>1.3739</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>27.372</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>2.474</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>12.8002</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>1.2635</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>5.5109</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>0.9816</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1.545</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>5.7551</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1.4068</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>40.6471</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>27.3772</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>30.4097</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>6.9927</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>17.0912</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>25.6601</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>4.2327</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>7.9063</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>42.5903</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>29.0609</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>13.587</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>3.8264</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>4.1742</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.2615</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>28.4885</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>4.2167</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2.2743</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>19.9832</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>19.3149</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>48.9774</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>9.725899999999999</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>4.0119</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>27.3719</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>12.6609</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>5.73</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>28.3141</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>18.4428</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>18.5718</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>4.6482</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>5.7717</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>1.236</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>5.1741</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>3.9765</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>7.9359</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>499.8679</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>300.8713</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>204.6666</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>9.867699999999999</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>216.7637</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>39.2418</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>48.9605</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>2.1143</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>461.9343</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>345.5175</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>109.0363</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>16.4443</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>8.797800000000001</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>4.8938</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>227.9196</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>11.3672</v>
       </c>
     </row>
@@ -3963,735 +4249,799 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1.7529</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>198.1177</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2.6966</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1.5559</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>11.0471</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.7328</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.8605</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1.098</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>2.55</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>193.5656</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>143.5436</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>104.0127</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>64.07170000000001</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>2.798</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>10.1525</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>2.3093</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>3.6158</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>13.5197</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>21.5085</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>13.5925</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>10.9191</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>73.90519999999999</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>4.1886</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>5.0061</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>14.0257</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>7.6123</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>19.6274</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>15.4924</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>6.0507</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>7.1367</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>22.2252</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.2338</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>7.8026</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>24.2175</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.8938</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>3.9032</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>5.937</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>9.5541</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1.7644</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1.7973</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>3.9258</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.7654</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>11.2531</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>4.1069</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>4.0956</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>2.1944</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>1.2458</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>1.5278</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.3121</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.3492</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>1.7337</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>15.5456</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>205.9251</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>145.6427</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>15.7485</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>116.6315</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>85.0645</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>135.2248</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>34.3394</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>486.6168</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>150.4367</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>142.3979</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>146.6475</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>84.5761</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>82.01220000000001</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>11.2885</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>137.0457</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>29.3756</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>7.7289</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>46.8831</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>180.6886</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>13.6161</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>6.1493</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>17.4632</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>22.3015</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>19.2656</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>5.3294</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>49.1141</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>48.4836</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>24.0087</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>15.3459</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>5.0205</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>34.8261</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>15.374</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1.3561</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>186.365</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>17.3407</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2.7657</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>8.722</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>4.947</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>17.5571</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>1.2399</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>163.2998</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>183.2664</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>53.83</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>40.1286</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>54.7644</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>5.0599</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.3929</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>17.1227</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>14.0471</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2.3493</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>91.1795</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>59.6926</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>13.2762</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>4.2562</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>6.8193</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.1135</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>5.398</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>0.5425</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>60.4855</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>35.5448</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>8.7721</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>21.9938</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.0568</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.1149</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>54.0311</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>3.02</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>26.6315</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>40.904</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>63.5966</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>4.4633</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>25.4041</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>30.3099</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>46.0546</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0115</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>24.1802</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>41.3718</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>14.6835</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.4561</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.1267</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.169</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>13.4092</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>1.9622</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1.8564</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>102.6094</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.0984</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>28.8233</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>29.8281</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>3.3299</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>3.6316</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>19.7417</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>2.7477</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>54.744</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>4.948</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>25.6004</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>2.527</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>11.0218</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1.9632</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>3.09</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>11.5102</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>2.8136</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>81.2942</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>54.7544</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>60.8193</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>13.9853</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>34.1824</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>51.3202</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>8.465400000000001</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>15.8126</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>85.1807</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>58.1218</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>27.1741</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>7.6528</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>8.3484</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.5231</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>56.977</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>8.433400000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>4.5486</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>39.9663</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>38.6299</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>97.95480000000001</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>19.4518</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>8.0238</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>54.7438</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>25.3219</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>11.4601</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>56.6282</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>36.8857</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>37.1436</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>9.2964</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>11.5434</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>2.472</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>10.3481</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>7.953</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>15.8718</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>999.7358</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>601.7426</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>409.3333</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>19.7354</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>433.5275</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>78.48350000000001</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>97.92100000000001</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>4.2286</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>923.8687</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>691.0349</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>218.0726</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>32.8886</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>17.5956</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>9.787599999999999</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>455.8392</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>22.7345</v>
       </c>
     </row>
@@ -4701,736 +5051,1602 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>3.3304</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>376.4236</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>5.1236</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2.9562</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>20.9895</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1.3923</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1.6349</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>2.0862</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>4.8451</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>367.7747</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>272.7329</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>197.6241</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>121.7362</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>5.3162</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>19.2897</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>4.3876</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>6.8701</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>25.6874</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>40.8662</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>25.8258</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>20.7462</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>140.42</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>7.9583</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>9.511699999999999</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>26.6488</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>14.4635</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>37.2921</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>29.4355</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>11.4963</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>13.5598</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>42.228</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.4441</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>14.8249</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>46.0133</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1.6982</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>7.4161</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>11.2803</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>18.1527</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>3.3523</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>3.4148</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>7.4589</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>1.4542</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>21.3808</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>7.803</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>7.7816</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>4.1693</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>2.3669</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>2.9029</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>0.593</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>0.6635</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>3.2941</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>29.5367</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>391.2576</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>276.7211</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>29.9221</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>221.5998</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>161.6225</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>256.927</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>65.2448</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>924.5719</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>285.8298</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>270.556</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>278.6303</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>160.6946</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>155.8231</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>21.4481</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>260.3868</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>55.8136</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>14.6849</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>89.078</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>343.3083</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>25.8706</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>11.6837</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>33.1801</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>42.3729</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>36.6047</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>10.1259</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>93.3168</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>92.1189</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>45.6166</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>29.1572</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>9.5389</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>5.985</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>66.1695</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>29.2106</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2.5766</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>354.0935</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>32.9473</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>5.2548</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>16.5718</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>9.3992</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>33.3584</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>2.3558</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>310.2696</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>348.2062</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>102.2771</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>76.24420000000001</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>104.0524</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>9.613899999999999</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0.7465000000000001</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>32.533</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>26.6895</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>4.4637</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>173.241</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>113.416</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>25.2248</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>8.0869</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>12.9566</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.2157</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>10.2562</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>1.0308</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>114.9225</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>67.5352</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>16.6669</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>41.7882</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0.1079</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.2183</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>102.6591</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>5.738</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>50.5999</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>77.7176</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>120.8336</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>8.4803</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>48.2678</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>57.5888</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>87.5038</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>0.0219</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>45.9425</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>78.60639999999999</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>27.8986</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0.8665</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0.2407</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0.3211</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>25.4774</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>3.7282</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>3.5272</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>194.9579</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.187</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>54.7644</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>56.6733</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>6.3269</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>6.9001</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>37.5092</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>5.2207</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>104.0137</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>9.4011</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>48.6408</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>4.8014</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>20.9414</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>3.7301</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>5.871</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>21.8693</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>5.3458</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>154.4591</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>104.0334</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>115.5567</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>26.5721</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>64.9466</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>97.50839999999999</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>16.0842</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>30.0439</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>161.8433</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>110.4315</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>51.6308</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>14.5403</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>15.862</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>0.9939</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>108.2562</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>16.0235</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>8.642300000000001</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>75.93600000000001</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>73.3968</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>186.1141</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>36.9585</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>15.2452</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>104.0132</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>48.1116</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>21.7742</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>107.5936</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>70.08280000000001</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>70.5728</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>17.6632</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>21.9324</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>4.6968</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>19.6614</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>15.1107</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>30.1563</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1899.498</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>1143.3109</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>777.7332</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>37.4973</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>823.7021999999999</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>149.1187</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>186.05</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>8.0344</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>1755.3505</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>1312.9664</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>414.338</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>62.4883</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>33.4316</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>18.5964</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>866.0946</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>43.1955</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sgr</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ruminant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rmk</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>RuminantMeat</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vegoil</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>lea</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>c_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>brasil</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>indonesia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bolivia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>angola</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ivorycoast</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>malasya</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>paraguay</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>drc</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/0_External_data/DeDuCE_rework/tms_f_initial_shocks_DeDuCE.xlsx
+++ b/0_External_data/DeDuCE_rework/tms_f_initial_shocks_DeDuCE.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -57,7 +58,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,14 +462,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>New columns RuminantMeat, dairy, vegoil, lea, pdr, c_b: list_commodity in rework_functions.R includes them.</t>
+          <t>New columns RuminantMeat, dairy, vegoil, lea, pdr, c_b: list_commodity in the game script includes them.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sheet OLD_current_file = the file the model uses today.</t>
+          <t>Sheet OLD_current_file = the reverse-engineered rates of the first submission (kept for comparison; not used by the runs).</t>
         </is>
       </c>
     </row>
@@ -479,8 +480,15 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Built by 0_External_data/DeDuCE_rework/zenodo_v2.1/build_deduce_tables.py.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1036,7 +1044,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1838,7 +1846,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2640,7 +2648,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3442,7 +3450,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4244,7 +4252,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -5046,7 +5054,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -5848,7 +5856,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -6650,6 +6658,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>